--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.0375143238385</v>
+        <v>4.556096077623756</v>
       </c>
       <c r="D2" t="n">
-        <v>23.77054029051257</v>
+        <v>3.862712797208293</v>
       </c>
       <c r="E2" t="n">
-        <v>15.60543414795509</v>
+        <v>2.535883049042702</v>
       </c>
       <c r="F2" t="n">
-        <v>4.932083702272092</v>
+        <v>0.801463601619215</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.76246035537495</v>
+        <v>4.348899807748429</v>
       </c>
       <c r="D3" t="n">
-        <v>27.95686866993278</v>
+        <v>4.542991158864077</v>
       </c>
       <c r="E3" t="n">
-        <v>15.60543414795509</v>
+        <v>2.535883049042702</v>
       </c>
       <c r="F3" t="n">
-        <v>4.932083702272092</v>
+        <v>0.801463601619215</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.1704695909698</v>
+        <v>8.640201308532593</v>
       </c>
       <c r="D4" t="n">
-        <v>32.6441409779364</v>
+        <v>5.304672908914665</v>
       </c>
       <c r="E4" t="n">
-        <v>15.60543414795509</v>
+        <v>2.535883049042702</v>
       </c>
       <c r="F4" t="n">
-        <v>4.932083702272092</v>
+        <v>0.801463601619215</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.95811071388379</v>
+        <v>10.23069299100612</v>
       </c>
       <c r="D5" t="n">
-        <v>32.57158517677417</v>
+        <v>5.292882591225803</v>
       </c>
       <c r="E5" t="n">
-        <v>15.60543414795509</v>
+        <v>2.535883049042702</v>
       </c>
       <c r="F5" t="n">
-        <v>4.932083702272092</v>
+        <v>0.801463601619215</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.53723572086849</v>
+        <v>3.17480080464113</v>
       </c>
       <c r="D6" t="n">
-        <v>20.43962662934738</v>
+        <v>3.32143932726895</v>
       </c>
       <c r="E6" t="n">
-        <v>15.60543414795509</v>
+        <v>2.535883049042702</v>
       </c>
       <c r="F6" t="n">
-        <v>4.932083702272092</v>
+        <v>0.801463601619215</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.17242258727818</v>
+        <v>7.340518670432705</v>
       </c>
       <c r="D7" t="n">
-        <v>21.49600253535527</v>
+        <v>3.493100411995231</v>
       </c>
       <c r="E7" t="n">
-        <v>15.60543414795509</v>
+        <v>2.535883049042702</v>
       </c>
       <c r="F7" t="n">
-        <v>4.932083702272092</v>
+        <v>0.801463601619215</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
